--- a/Tagihan/2026/Juli/SDN Lukbayur.xlsx
+++ b/Tagihan/2026/Juli/SDN Lukbayur.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{183817EA-759F-41FF-8BBE-1AD9E545E0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAEDF69-41DA-4C73-B717-CC095A0063CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="720" windowWidth="19410" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1176,11 +1176,11 @@
         <v>27</v>
       </c>
       <c r="F17" s="27">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="G17" s="28">
         <f>D17*F17</f>
-        <v>1300000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1197,11 +1197,11 @@
         <v>18</v>
       </c>
       <c r="F18" s="29">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="G18" s="28">
         <f t="shared" ref="G18:G23" si="0">D18*F18</f>
-        <v>745000</v>
+        <v>596000</v>
       </c>
     </row>
     <row r="19" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1367,7 +1367,7 @@
       <c r="F30" s="46"/>
       <c r="G30" s="31">
         <f>SUM(G17:G29)</f>
-        <v>2605000</v>
+        <v>2356000</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
